--- a/benchmarks/attachment_intelligence/fixtures/files/f30.xlsx
+++ b/benchmarks/attachment_intelligence/fixtures/files/f30.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шайба M10</t>
+          <t xml:space="preserve">Шайба DIN125 M10 цинк</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
